--- a/WikiRace_題庫總表.xlsx
+++ b/WikiRace_題庫總表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,50 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>台灣 -&gt; 臺灣猶太人歷史 -&gt; 中華人民共和國 -&gt; 江苏省 -&gt; 丹阳市</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-29 18:48:57</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>台灣</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>南塭_(花嶼)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>台灣 -&gt; 花瓶嶼 -&gt; 海翁礁 -&gt; 毛常嶼 -&gt; 雞母塢塭 -&gt; 南塭_(花嶼)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-29 19:01:58</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>馬力歐</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>向下相容</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>馬力歐 -&gt; Game_Boy -&gt; ROM卡带 -&gt; 雅達利XEGS -&gt; 向下相容</t>
         </is>
       </c>
     </row>

--- a/WikiRace_題庫總表.xlsx
+++ b/WikiRace_題庫總表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,6 +501,28 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>馬力歐 -&gt; Game_Boy -&gt; ROM卡带 -&gt; 雅達利XEGS -&gt; 向下相容</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:34:26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>元智大學</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>臺灣體大足球隊</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>元智大學 -&gt; 中華醫事科技大學 -&gt; 台南神學院 -&gt; 高雄 -&gt; 台電足球隊 -&gt; 臺灣體大足球隊</t>
         </is>
       </c>
     </row>
